--- a/workshop_manager.xlsx
+++ b/workshop_manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coolname/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817A9830-83B0-4345-AF48-3E299CBDD0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B69034-08FD-B048-9947-F72A40963C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9420" yWindow="600" windowWidth="24600" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Workshop Manager" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
   <si>
     <t>CARPLA SERVICE — QUẢN LÝ XƯỞNG &amp; FILE DỮ LIỆU</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Tân Cảng</t>
-  </si>
-  <si>
-    <t>Chờ dữ liệu</t>
   </si>
   <si>
     <t>Điền tên file và target sau khi có dữ liệu</t>
@@ -676,10 +673,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="8">
@@ -709,13 +706,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="H4" s="9">
         <v>552</v>
@@ -724,10 +721,10 @@
         <v>1104000000</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1156,7 +1153,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1166,19 +1163,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>10</v>
@@ -1189,19 +1186,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30">
@@ -1209,19 +1206,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="20" t="s">
         <v>33</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -1229,19 +1226,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -1249,19 +1246,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30">
@@ -1269,19 +1266,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
